--- a/tests/Data/APEXPAllState.xlsx
+++ b/tests/Data/APEXPAllState.xlsx
@@ -416,7 +416,7 @@
     <t xml:space="preserve">Seneca Insurance Company, Inc.</t>
   </si>
   <si>
-    <t xml:space="preserve">123 North Dakota ND usa</t>
+    <t xml:space="preserve">North Dakota ND usa</t>
   </si>
   <si>
     <t xml:space="preserve">30</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">Endurance Assurance Corporation</t>
   </si>
   <si>
-    <t xml:space="preserve">123 New York NY usa</t>
+    <t xml:space="preserve">New York NY usa</t>
   </si>
   <si>
     <t xml:space="preserve">35</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">Pennsylvania Manufacturers' Association Insurance Company</t>
   </si>
   <si>
-    <t xml:space="preserve">Meridion utah ut usa</t>
+    <t xml:space="preserve">Meridion Health utah ut usa</t>
   </si>
   <si>
     <t xml:space="preserve">45</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">SOUTHWEST MARINE AND GENERAL INSURANCE COMPANY</t>
   </si>
   <si>
-    <t xml:space="preserve">Meridian virginia usa</t>
+    <t xml:space="preserve">Meridian park virginia usa</t>
   </si>
   <si>
     <t xml:space="preserve">46</t>

--- a/tests/Data/APEXPAllState.xlsx
+++ b/tests/Data/APEXPAllState.xlsx
@@ -593,7 +593,7 @@
     <t xml:space="preserve">First Founders Assurance Company</t>
   </si>
   <si>
-    <t xml:space="preserve">123 South Carolina SC usa</t>
+    <t xml:space="preserve">123 South SC usa</t>
   </si>
   <si>
     <t xml:space="preserve">41</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">SOUTHWEST MARINE AND GENERAL INSURANCE COMPANY</t>
   </si>
   <si>
-    <t xml:space="preserve">Meridian park virginia usa</t>
+    <t xml:space="preserve">123 Medical VA USA</t>
   </si>
   <si>
     <t xml:space="preserve">46</t>

--- a/tests/Data/APEXPAllState.xlsx
+++ b/tests/Data/APEXPAllState.xlsx
@@ -164,7 +164,7 @@
     <t xml:space="preserve">AMERICAN CONTRACTORS INDEMNITY COMPANY</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Delaware DE usa</t>
+    <t xml:space="preserve"> Delaware DE usa</t>
   </si>
   <si>
     <t xml:space="preserve">14</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">s</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Indiana IN usa</t>
+    <t xml:space="preserve"> Indiana IN usa</t>
   </si>
   <si>
     <t xml:space="preserve">20</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">SOUTHWEST MARINE AND GENERAL INSURANCE COMPANY</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Medical VA USA</t>
+    <t xml:space="preserve">Medical VA USA</t>
   </si>
   <si>
     <t xml:space="preserve">46</t>
